--- a/data/trans_orig/P77_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P77_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según cual es la persona sustentadora principal del hogar en 2023</t>
+          <t>Población según cual es la persona sustentadora principal del hogar en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>25786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>58163</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60817</t>
+          <t>60294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>90273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93369</t>
+          <t>94335</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136903</t>
+          <t>136417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,47 +878,47 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>6400</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2119</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5670</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2119</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>447762</t>
+          <t>447049</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>480236</t>
+          <t>479426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>354585</t>
+          <t>354700</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>384855</t>
+          <t>385430</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>812362</t>
+          <t>813311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>856119</t>
+          <t>856023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13758</t>
+          <t>14949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58725</t>
+          <t>58917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84851</t>
+          <t>86539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79226</t>
+          <t>79042</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113477</t>
+          <t>112476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -1299,97 +1299,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3984</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1187</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4073</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>4268</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>417248</t>
+          <t>415390</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>438455</t>
+          <t>437264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>296643</t>
+          <t>294849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>323144</t>
+          <t>322353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>720242</t>
+          <t>720269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>755025</t>
+          <t>754248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45163</t>
+          <t>44071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42385</t>
+          <t>43572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62636</t>
+          <t>61744</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>34140</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114807</t>
+          <t>114743</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1755,97 +1755,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2624</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>623101</t>
+          <t>624193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>660209</t>
+          <t>660453</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104275</t>
+          <t>105167</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124526</t>
+          <t>123339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720368</t>
+          <t>720432</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>804965</t>
+          <t>801035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88560</t>
+          <t>87520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>149077</t>
+          <t>150210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>278528</t>
+          <t>280482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>689272</t>
+          <t>655180</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>369557</t>
+          <t>374347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>956974</t>
+          <t>1025419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>882486</t>
+          <t>883552</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>944008</t>
+          <t>944938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>288095</t>
+          <t>321704</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>697928</t>
+          <t>695210</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1053798</t>
+          <t>987261</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1639364</t>
+          <t>1634227</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41028</t>
+          <t>42127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>81904</t>
+          <t>80442</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191632</t>
+          <t>198822</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295992</t>
+          <t>301474</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>259896</t>
+          <t>258767</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>354914</t>
+          <t>354903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12625</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>943</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>11236</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>390007</t>
+          <t>390535</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>431050</t>
+          <t>431072</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>544816</t>
+          <t>539778</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>649086</t>
+          <t>642424</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>957793</t>
+          <t>958372</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1052999</t>
+          <t>1056374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>228405</t>
+          <t>225162</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>743825</t>
+          <t>744707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>757380</t>
+          <t>757567</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>979032</t>
+          <t>979321</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>996480</t>
+          <t>996493</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3236,97 +3236,97 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3212</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>548</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3111</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>3199</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2778</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>395048</t>
+          <t>391126</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>570538</t>
+          <t>575960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1487108</t>
+          <t>1497303</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1993180</t>
+          <t>1997577</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1915897</t>
+          <t>1912142</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2624709</t>
+          <t>2640780</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>20175</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>21567</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>33421</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2796683</t>
+          <t>2792233</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2976288</t>
+          <t>2979083</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1569467</t>
+          <t>1563696</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2074602</t>
+          <t>2066982</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4326629</t>
+          <t>4294095</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5018648</t>
+          <t>5022870</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
